--- a/excel_routes/route_RUH_ATZ_threats.xlsx
+++ b/excel_routes/route_RUH_ATZ_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CF46BD-EB11-45B2-8E8A-B0C3B8CCD62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB8036F-1851-4F34-B3CE-DBBC6EFCA4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -135,18 +135,18 @@
     <t>02-SEP-26</t>
   </si>
   <si>
-    <t>flynas XY-267</t>
+    <t>flynas XY-271</t>
   </si>
   <si>
     <t>08-SEP-26</t>
   </si>
   <si>
+    <t>09-SEP-26</t>
+  </si>
+  <si>
     <t>flynas XY-265</t>
   </si>
   <si>
-    <t>09-SEP-26</t>
-  </si>
-  <si>
     <t>15-SEP-26</t>
   </si>
   <si>
@@ -156,70 +156,34 @@
     <t>22-SEP-26</t>
   </si>
   <si>
-    <t>29-SEP-26</t>
-  </si>
-  <si>
-    <t>30-SEP-26</t>
-  </si>
-  <si>
     <t>06-OCT-26</t>
   </si>
   <si>
+    <t>flynas XY-273</t>
+  </si>
+  <si>
+    <t>Air Arabia Egypt E5-411</t>
+  </si>
+  <si>
     <t>07-OCT-26</t>
   </si>
   <si>
     <t>13-OCT-26</t>
   </si>
   <si>
-    <t>flynas XY-273</t>
-  </si>
-  <si>
-    <t>14-OCT-26</t>
-  </si>
-  <si>
-    <t>Air Arabia Egypt E5-411</t>
+    <t>20-OCT-26</t>
   </si>
   <si>
     <t>21-OCT-26</t>
   </si>
   <si>
-    <t>28-OCT-26</t>
-  </si>
-  <si>
-    <t>31-OCT-26</t>
-  </si>
-  <si>
     <t>28-NOV-26</t>
   </si>
   <si>
+    <t>12-DEC-26</t>
+  </si>
+  <si>
     <t>flynas XY-287</t>
-  </si>
-  <si>
-    <t>02-DEC-26</t>
-  </si>
-  <si>
-    <t>05-DEC-26</t>
-  </si>
-  <si>
-    <t>09-DEC-26</t>
-  </si>
-  <si>
-    <t>Saudia SV-311</t>
-  </si>
-  <si>
-    <t>12-DEC-26</t>
-  </si>
-  <si>
-    <t>16-DEC-26</t>
-  </si>
-  <si>
-    <t>19-DEC-26</t>
-  </si>
-  <si>
-    <t>26-DEC-26</t>
-  </si>
-  <si>
-    <t>30-DEC-26</t>
   </si>
 </sst>
 </file>
@@ -616,7 +580,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1167,13 +1131,13 @@
         <v>27</v>
       </c>
       <c r="D16" s="2">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="E16" s="2">
         <v>552</v>
       </c>
       <c r="F16" s="2">
-        <v>-151</v>
+        <v>-121</v>
       </c>
       <c r="G16" s="2">
         <v>46</v>
@@ -1832,13 +1796,13 @@
         <v>17</v>
       </c>
       <c r="D35" s="2">
-        <v>500</v>
+        <v>416</v>
       </c>
       <c r="E35" s="2">
         <v>739</v>
       </c>
       <c r="F35" s="2">
-        <v>-239</v>
+        <v>-323</v>
       </c>
       <c r="G35" s="2">
         <v>40</v>
@@ -1849,8 +1813,8 @@
       <c r="I35" s="2">
         <v>-10</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>14</v>
+      <c r="J35" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>15</v>
@@ -1864,16 +1828,16 @@
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D36" s="2">
-        <v>610</v>
+        <v>524</v>
       </c>
       <c r="E36" s="2">
         <v>739</v>
       </c>
       <c r="F36" s="2">
-        <v>-129</v>
+        <v>-215</v>
       </c>
       <c r="G36" s="2">
         <v>40</v>
@@ -1899,28 +1863,28 @@
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D37" s="2">
-        <v>644</v>
+        <v>544</v>
       </c>
       <c r="E37" s="2">
         <v>739</v>
       </c>
       <c r="F37" s="2">
-        <v>-95</v>
+        <v>-195</v>
       </c>
       <c r="G37" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2">
         <v>30</v>
       </c>
       <c r="I37" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>15</v>
@@ -1998,31 +1962,31 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D40" s="2">
-        <v>644</v>
+        <v>329</v>
       </c>
       <c r="E40" s="2">
-        <v>739</v>
+        <v>805</v>
       </c>
       <c r="F40" s="2">
-        <v>-95</v>
+        <v>-476</v>
       </c>
       <c r="G40" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H40" s="2">
         <v>30</v>
       </c>
       <c r="I40" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>14</v>
@@ -2033,7 +1997,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>12</v>
@@ -2068,31 +2032,31 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D42" s="2">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="E42" s="2">
         <v>805</v>
       </c>
       <c r="F42" s="2">
-        <v>-207</v>
+        <v>-195</v>
       </c>
       <c r="G42" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H42" s="2">
         <v>30</v>
       </c>
       <c r="I42" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>14</v>
@@ -2103,22 +2067,22 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D43" s="2">
-        <v>610</v>
+        <v>416</v>
       </c>
       <c r="E43" s="2">
-        <v>805</v>
+        <v>739</v>
       </c>
       <c r="F43" s="2">
-        <v>-195</v>
+        <v>-323</v>
       </c>
       <c r="G43" s="2">
         <v>40</v>
@@ -2129,8 +2093,8 @@
       <c r="I43" s="2">
         <v>-10</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>14</v>
+      <c r="J43" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>15</v>
@@ -2144,7 +2108,7 @@
         <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D44" s="2">
         <v>416</v>
@@ -2173,22 +2137,22 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D45" s="2">
         <v>416</v>
       </c>
       <c r="E45" s="2">
-        <v>739</v>
+        <v>673</v>
       </c>
       <c r="F45" s="2">
-        <v>-323</v>
+        <v>-257</v>
       </c>
       <c r="G45" s="2">
         <v>40</v>
@@ -2208,34 +2172,34 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D46" s="2">
-        <v>619</v>
+        <v>416</v>
       </c>
       <c r="E46" s="2">
-        <v>739</v>
+        <v>673</v>
       </c>
       <c r="F46" s="2">
-        <v>-120</v>
+        <v>-257</v>
       </c>
       <c r="G46" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H46" s="2">
         <v>30</v>
       </c>
       <c r="I46" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>14</v>
+        <v>-10</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>15</v>
@@ -2243,22 +2207,22 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D47" s="2">
-        <v>416</v>
+        <v>500</v>
       </c>
       <c r="E47" s="2">
-        <v>673</v>
+        <v>739</v>
       </c>
       <c r="F47" s="2">
-        <v>-257</v>
+        <v>-239</v>
       </c>
       <c r="G47" s="2">
         <v>40</v>
@@ -2269,8 +2233,8 @@
       <c r="I47" s="2">
         <v>-10</v>
       </c>
-      <c r="J47" s="4" t="s">
-        <v>22</v>
+      <c r="J47" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>15</v>
@@ -2278,7 +2242,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>12</v>
@@ -2287,13 +2251,13 @@
         <v>17</v>
       </c>
       <c r="D48" s="2">
-        <v>416</v>
+        <v>610</v>
       </c>
       <c r="E48" s="2">
-        <v>673</v>
+        <v>739</v>
       </c>
       <c r="F48" s="2">
-        <v>-257</v>
+        <v>-129</v>
       </c>
       <c r="G48" s="2">
         <v>40</v>
@@ -2304,8 +2268,8 @@
       <c r="I48" s="2">
         <v>-10</v>
       </c>
-      <c r="J48" s="4" t="s">
-        <v>22</v>
+      <c r="J48" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>15</v>
@@ -2313,31 +2277,31 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D49" s="2">
-        <v>544</v>
+        <v>500</v>
       </c>
       <c r="E49" s="2">
-        <v>673</v>
+        <v>739</v>
       </c>
       <c r="F49" s="2">
-        <v>-129</v>
+        <v>-239</v>
       </c>
       <c r="G49" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H49" s="2">
         <v>30</v>
       </c>
       <c r="I49" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>14</v>
@@ -2348,22 +2312,22 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D50" s="2">
-        <v>500</v>
+        <v>524</v>
       </c>
       <c r="E50" s="2">
         <v>739</v>
       </c>
       <c r="F50" s="2">
-        <v>-239</v>
+        <v>-215</v>
       </c>
       <c r="G50" s="2">
         <v>40</v>
@@ -2383,22 +2347,22 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D51" s="2">
-        <v>610</v>
+        <v>676</v>
       </c>
       <c r="E51" s="2">
         <v>739</v>
       </c>
       <c r="F51" s="2">
-        <v>-129</v>
+        <v>-63</v>
       </c>
       <c r="G51" s="2">
         <v>40</v>
@@ -2418,31 +2382,31 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D52" s="2">
-        <v>601</v>
+        <v>500</v>
       </c>
       <c r="E52" s="2">
-        <v>571</v>
+        <v>739</v>
       </c>
       <c r="F52" s="2">
-        <v>30</v>
+        <v>-239</v>
       </c>
       <c r="G52" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H52" s="2">
         <v>30</v>
       </c>
       <c r="I52" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>14</v>
@@ -2453,31 +2417,31 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="D53" s="2">
-        <v>601</v>
+        <v>524</v>
       </c>
       <c r="E53" s="2">
-        <v>571</v>
+        <v>739</v>
       </c>
       <c r="F53" s="2">
-        <v>30</v>
+        <v>-215</v>
       </c>
       <c r="G53" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H53" s="2">
         <v>30</v>
       </c>
       <c r="I53" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>14</v>
@@ -2488,13 +2452,13 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D54" s="2">
         <v>500</v>
@@ -2523,31 +2487,31 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="D55" s="2">
-        <v>601</v>
+        <v>676</v>
       </c>
       <c r="E55" s="2">
         <v>739</v>
       </c>
       <c r="F55" s="2">
-        <v>-138</v>
+        <v>-63</v>
       </c>
       <c r="G55" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H55" s="2">
         <v>30</v>
       </c>
       <c r="I55" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>14</v>
@@ -2558,7 +2522,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>12</v>
@@ -2593,31 +2557,31 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D57" s="2">
-        <v>601</v>
+        <v>644</v>
       </c>
       <c r="E57" s="2">
         <v>739</v>
       </c>
       <c r="F57" s="2">
-        <v>-138</v>
+        <v>-95</v>
       </c>
       <c r="G57" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H57" s="2">
         <v>30</v>
       </c>
       <c r="I57" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>14</v>
@@ -2628,13 +2592,13 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D58" s="2">
         <v>644</v>
@@ -2658,741 +2622,6 @@
         <v>14</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D59" s="2">
-        <v>644</v>
-      </c>
-      <c r="E59" s="2">
-        <v>739</v>
-      </c>
-      <c r="F59" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G59" s="2">
-        <v>40</v>
-      </c>
-      <c r="H59" s="2">
-        <v>30</v>
-      </c>
-      <c r="I59" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D60" s="2">
-        <v>644</v>
-      </c>
-      <c r="E60" s="2">
-        <v>739</v>
-      </c>
-      <c r="F60" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G60" s="2">
-        <v>40</v>
-      </c>
-      <c r="H60" s="2">
-        <v>30</v>
-      </c>
-      <c r="I60" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D61" s="2">
-        <v>679</v>
-      </c>
-      <c r="E61" s="2">
-        <v>739</v>
-      </c>
-      <c r="F61" s="2">
-        <v>-60</v>
-      </c>
-      <c r="G61" s="2">
-        <v>40</v>
-      </c>
-      <c r="H61" s="2">
-        <v>30</v>
-      </c>
-      <c r="I61" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D62" s="2">
-        <v>684</v>
-      </c>
-      <c r="E62" s="2">
-        <v>739</v>
-      </c>
-      <c r="F62" s="2">
-        <v>-55</v>
-      </c>
-      <c r="G62" s="2">
-        <v>40</v>
-      </c>
-      <c r="H62" s="2">
-        <v>30</v>
-      </c>
-      <c r="I62" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D63" s="2">
-        <v>684</v>
-      </c>
-      <c r="E63" s="2">
-        <v>739</v>
-      </c>
-      <c r="F63" s="2">
-        <v>-55</v>
-      </c>
-      <c r="G63" s="2">
-        <v>40</v>
-      </c>
-      <c r="H63" s="2">
-        <v>30</v>
-      </c>
-      <c r="I63" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" s="2">
-        <v>500</v>
-      </c>
-      <c r="E64" s="2">
-        <v>739</v>
-      </c>
-      <c r="F64" s="2">
-        <v>-239</v>
-      </c>
-      <c r="G64" s="2">
-        <v>30</v>
-      </c>
-      <c r="H64" s="2">
-        <v>30</v>
-      </c>
-      <c r="I64" s="2">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" s="2">
-        <v>601</v>
-      </c>
-      <c r="E65" s="2">
-        <v>739</v>
-      </c>
-      <c r="F65" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G65" s="2">
-        <v>46</v>
-      </c>
-      <c r="H65" s="2">
-        <v>30</v>
-      </c>
-      <c r="I65" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D66" s="2">
-        <v>601</v>
-      </c>
-      <c r="E66" s="2">
-        <v>739</v>
-      </c>
-      <c r="F66" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G66" s="2">
-        <v>46</v>
-      </c>
-      <c r="H66" s="2">
-        <v>30</v>
-      </c>
-      <c r="I66" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D67" s="2">
-        <v>644</v>
-      </c>
-      <c r="E67" s="2">
-        <v>739</v>
-      </c>
-      <c r="F67" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G67" s="2">
-        <v>40</v>
-      </c>
-      <c r="H67" s="2">
-        <v>30</v>
-      </c>
-      <c r="I67" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D68" s="2">
-        <v>676</v>
-      </c>
-      <c r="E68" s="2">
-        <v>739</v>
-      </c>
-      <c r="F68" s="2">
-        <v>-63</v>
-      </c>
-      <c r="G68" s="2">
-        <v>46</v>
-      </c>
-      <c r="H68" s="2">
-        <v>30</v>
-      </c>
-      <c r="I68" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D69" s="2">
-        <v>601</v>
-      </c>
-      <c r="E69" s="2">
-        <v>739</v>
-      </c>
-      <c r="F69" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G69" s="2">
-        <v>46</v>
-      </c>
-      <c r="H69" s="2">
-        <v>30</v>
-      </c>
-      <c r="I69" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D70" s="2">
-        <v>601</v>
-      </c>
-      <c r="E70" s="2">
-        <v>739</v>
-      </c>
-      <c r="F70" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G70" s="2">
-        <v>46</v>
-      </c>
-      <c r="H70" s="2">
-        <v>30</v>
-      </c>
-      <c r="I70" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D71" s="2">
-        <v>644</v>
-      </c>
-      <c r="E71" s="2">
-        <v>739</v>
-      </c>
-      <c r="F71" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G71" s="2">
-        <v>40</v>
-      </c>
-      <c r="H71" s="2">
-        <v>30</v>
-      </c>
-      <c r="I71" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D72" s="2">
-        <v>601</v>
-      </c>
-      <c r="E72" s="2">
-        <v>739</v>
-      </c>
-      <c r="F72" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G72" s="2">
-        <v>46</v>
-      </c>
-      <c r="H72" s="2">
-        <v>30</v>
-      </c>
-      <c r="I72" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D73" s="2">
-        <v>638</v>
-      </c>
-      <c r="E73" s="2">
-        <v>739</v>
-      </c>
-      <c r="F73" s="2">
-        <v>-101</v>
-      </c>
-      <c r="G73" s="2">
-        <v>46</v>
-      </c>
-      <c r="H73" s="2">
-        <v>30</v>
-      </c>
-      <c r="I73" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D74" s="2">
-        <v>601</v>
-      </c>
-      <c r="E74" s="2">
-        <v>739</v>
-      </c>
-      <c r="F74" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G74" s="2">
-        <v>46</v>
-      </c>
-      <c r="H74" s="2">
-        <v>30</v>
-      </c>
-      <c r="I74" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K74" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D75" s="2">
-        <v>601</v>
-      </c>
-      <c r="E75" s="2">
-        <v>739</v>
-      </c>
-      <c r="F75" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G75" s="2">
-        <v>46</v>
-      </c>
-      <c r="H75" s="2">
-        <v>30</v>
-      </c>
-      <c r="I75" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K75" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D76" s="2">
-        <v>601</v>
-      </c>
-      <c r="E76" s="2">
-        <v>739</v>
-      </c>
-      <c r="F76" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G76" s="2">
-        <v>46</v>
-      </c>
-      <c r="H76" s="2">
-        <v>30</v>
-      </c>
-      <c r="I76" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D77" s="2">
-        <v>601</v>
-      </c>
-      <c r="E77" s="2">
-        <v>739</v>
-      </c>
-      <c r="F77" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G77" s="2">
-        <v>46</v>
-      </c>
-      <c r="H77" s="2">
-        <v>30</v>
-      </c>
-      <c r="I77" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D78" s="2">
-        <v>601</v>
-      </c>
-      <c r="E78" s="2">
-        <v>739</v>
-      </c>
-      <c r="F78" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G78" s="2">
-        <v>46</v>
-      </c>
-      <c r="H78" s="2">
-        <v>30</v>
-      </c>
-      <c r="I78" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D79" s="2">
-        <v>684</v>
-      </c>
-      <c r="E79" s="2">
-        <v>739</v>
-      </c>
-      <c r="F79" s="2">
-        <v>-55</v>
-      </c>
-      <c r="G79" s="2">
-        <v>40</v>
-      </c>
-      <c r="H79" s="2">
-        <v>30</v>
-      </c>
-      <c r="I79" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K79" s="2" t="s">
         <v>15</v>
       </c>
     </row>
